--- a/output/lmm_late.xlsx
+++ b/output/lmm_late.xlsx
@@ -579,49 +579,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.656</v>
+        <v>24.262</v>
       </c>
       <c r="C4" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.261</v>
+        <v>0.063</v>
       </c>
       <c r="F4" t="n">
-        <v>0.377</v>
+        <v>0.204</v>
       </c>
       <c r="G4" t="n">
-        <v>0.492</v>
+        <v>0.2549999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.049</v>
+        <v>1.423</v>
       </c>
       <c r="I4" t="n">
-        <v>0.926</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.926</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.018</v>
+        <v>-0.004</v>
       </c>
       <c r="L4" t="n">
-        <v>0.928</v>
+        <v>0.722</v>
       </c>
       <c r="M4" t="n">
-        <v>0.928</v>
+        <v>0.722</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="O4" t="n">
-        <v>0.905</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -631,30 +631,50 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.295</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+        <v>4.33</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+        <v>0.022</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2549999999999999</v>
+      </c>
       <c r="H5" t="n">
-        <v>1.084</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>2.329</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>-0.049</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.005</v>
+      </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -663,30 +683,50 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.61</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+        <v>11.729</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+        <v>0.006</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.846</v>
+      </c>
       <c r="H6" t="n">
-        <v>1.086</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>1.879</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
       <c r="K6" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>-0.039</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.015</v>
+      </c>
       <c r="N6" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -695,7 +735,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.105</v>
+        <v>1.94</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -704,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.064</v>
+        <v>0.041</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -713,24 +753,32 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.033</v>
+        <v>1.72</v>
       </c>
       <c r="I7" t="n">
-        <v>0.326</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.926</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>0.05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -739,49 +787,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.147</v>
+        <v>4.33</v>
       </c>
       <c r="C8" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.042</v>
+        <v>-0.018</v>
       </c>
       <c r="F8" t="n">
-        <v>0.492</v>
+        <v>0.185</v>
       </c>
       <c r="G8" t="n">
-        <v>0.492</v>
+        <v>0.2549999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.873</v>
+        <v>2.271</v>
       </c>
       <c r="I8" t="n">
-        <v>0.745</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.926</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.019</v>
+        <v>-0.011</v>
       </c>
       <c r="L8" t="n">
-        <v>0.657</v>
+        <v>0.364</v>
       </c>
       <c r="M8" t="n">
-        <v>0.928</v>
+        <v>0.455</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="O8" t="n">
-        <v>0.621</v>
+        <v>0.001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.905</v>
+        <v>0.001</v>
       </c>
     </row>
   </sheetData>
